--- a/diseases/d165/2005-2009.xlsx
+++ b/diseases/d165/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>3</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -2841,9 +2832,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -3533,9 +3521,6 @@
       <c r="O18" t="n">
         <v>5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -4225,9 +4210,6 @@
       <c r="O22" t="n">
         <v>5</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -4917,9 +4899,6 @@
       <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.07624737851981726</v>
       </c>
@@ -5609,9 +5588,6 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -6301,9 +6277,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -6993,9 +6966,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -7685,9 +7655,6 @@
       <c r="O42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -8377,9 +8344,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9069,9 +9033,6 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -9761,9 +9722,6 @@
       <c r="O54" t="n">
         <v>2</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -10453,9 +10411,6 @@
       <c r="O58" t="n">
         <v>2</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -11145,9 +11100,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -11837,9 +11789,6 @@
       <c r="O66" t="n">
         <v>4</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -12529,9 +12478,6 @@
       <c r="O70" t="n">
         <v>4</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -13221,9 +13167,6 @@
       <c r="O74" t="n">
         <v>4</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -13913,9 +13856,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -14605,9 +14545,6 @@
       <c r="O82" t="n">
         <v>2</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -15297,9 +15234,6 @@
       <c r="O86" t="n">
         <v>3</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -15989,9 +15923,6 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -16681,9 +16612,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17373,9 +17301,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -18065,9 +17990,6 @@
       <c r="O102" t="n">
         <v>3</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -18757,9 +18679,6 @@
       <c r="O106" t="n">
         <v>4</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -19449,9 +19368,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -20141,9 +20057,6 @@
       <c r="O114" t="n">
         <v>4</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -20833,9 +20746,6 @@
       <c r="O118" t="n">
         <v>2</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -21525,9 +21435,6 @@
       <c r="O122" t="n">
         <v>4</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -22217,9 +22124,6 @@
       <c r="O126" t="n">
         <v>3</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -22909,9 +22813,6 @@
       <c r="O130" t="n">
         <v>4</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.07563281026942298</v>
       </c>
@@ -23601,9 +23502,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -24293,9 +24191,6 @@
       <c r="O138" t="n">
         <v>3</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.05672460770206724</v>
       </c>
@@ -24985,9 +24880,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -25677,9 +25569,6 @@
       <c r="O146" t="n">
         <v>3</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -26369,9 +26258,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -27061,9 +26947,6 @@
       <c r="O154" t="n">
         <v>4</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.07528168996854542</v>
       </c>
@@ -27753,9 +27636,6 @@
       <c r="O158" t="n">
         <v>5</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -28445,9 +28325,6 @@
       <c r="O162" t="n">
         <v>6</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -29137,9 +29014,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -29829,9 +29703,6 @@
       <c r="O170" t="n">
         <v>3</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.05646126747640907</v>
       </c>
@@ -30521,9 +30392,6 @@
       <c r="O174" t="n">
         <v>6</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -31213,9 +31081,6 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -31905,9 +31770,6 @@
       <c r="O182" t="n">
         <v>6</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.1129225349528181</v>
       </c>
@@ -32597,9 +32459,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -33289,9 +33148,6 @@
       <c r="O190" t="n">
         <v>5</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.09410211246068179</v>
       </c>
@@ -33981,9 +33837,6 @@
       <c r="O194" t="n">
         <v>7</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.1311142189343355</v>
       </c>
@@ -34673,9 +34526,6 @@
       <c r="O198" t="n">
         <v>2</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -35365,9 +35215,6 @@
       <c r="O202" t="n">
         <v>6</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.1123836162294304</v>
       </c>
@@ -36057,9 +35904,6 @@
       <c r="O206" t="n">
         <v>3</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -36749,9 +36593,6 @@
       <c r="O210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -37441,9 +37282,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -38133,9 +37971,6 @@
       <c r="O218" t="n">
         <v>5</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.09365301352452535</v>
       </c>
@@ -38825,9 +38660,6 @@
       <c r="O222" t="n">
         <v>4</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -39517,9 +39349,6 @@
       <c r="O226" t="n">
         <v>4</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -40209,9 +40038,6 @@
       <c r="O230" t="n">
         <v>2</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -40901,9 +40727,6 @@
       <c r="O234" t="n">
         <v>5</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.09365301352452535</v>
       </c>
@@ -41592,9 +41415,6 @@
       </c>
       <c r="O238" t="n">
         <v>1</v>
-      </c>
-      <c r="Q238" t="n">
-        <v>0</v>
       </c>
       <c r="R238" t="n">
         <v>0.01873060270490507</v>
